--- a/test/branch2.xlsx
+++ b/test/branch2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhiraj Das\Documents\DMSBackend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEBEFC42-7BD2-4C96-90A2-02605463C2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A0B095-1303-4375-AAE4-C917C696D2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>client</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>branch_name</t>
   </si>
@@ -64,14 +61,23 @@
     <t>India</t>
   </si>
   <si>
-    <t>Branch A</t>
+    <t>124 Street, Area A</t>
+  </si>
+  <si>
+    <t>27ABCDE1234F1Z6</t>
+  </si>
+  <si>
+    <t>client_id</t>
+  </si>
+  <si>
+    <t>Malad</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,6 +89,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -432,68 +444,98 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2">
         <v>9876543210</v>
       </c>
       <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
       </c>
       <c r="I2">
         <v>400001</v>
       </c>
     </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>9876543210</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3">
+        <v>400001</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/test/branch2.xlsx
+++ b/test/branch2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhiraj Das\Documents\DMSBackend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A0B095-1303-4375-AAE4-C917C696D2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360FE76C-A679-4F62-9030-5947439FE522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>branch_name</t>
   </si>
@@ -71,13 +71,16 @@
   </si>
   <si>
     <t>Malad</t>
+  </si>
+  <si>
+    <t>I@di@</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -95,6 +98,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -132,16 +143,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -498,8 +512,8 @@
       <c r="G2" t="s">
         <v>11</v>
       </c>
-      <c r="H2" t="s">
-        <v>12</v>
+      <c r="H2" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="I2">
         <v>400001</v>
@@ -536,6 +550,9 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{C291B3D8-A033-43AA-9CD1-EE78AA504898}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>